--- a/data/preparation/puma_pre.xlsx
+++ b/data/preparation/puma_pre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/justinanointinggabriel/Documents/Gabe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE527377-EEA1-E646-A135-7B30D63A2467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB9BB387-26DC-264C-9B75-581D471DFB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7580" yWindow="600" windowWidth="21220" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="245">
   <si>
     <t>ID</t>
   </si>
@@ -750,6 +750,45 @@
   </si>
   <si>
     <t>DEU25P00-15</t>
+  </si>
+  <si>
+    <t>STAKE</t>
+  </si>
+  <si>
+    <t>CHALL</t>
+  </si>
+  <si>
+    <t>MARKET</t>
+  </si>
+  <si>
+    <t>STRAT</t>
+  </si>
+  <si>
+    <t>PEOPLE</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>PERF</t>
+  </si>
+  <si>
+    <t>START</t>
+  </si>
+  <si>
+    <t>negative</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative </t>
+  </si>
+  <si>
+    <t xml:space="preserve">neutral </t>
   </si>
 </sst>
 </file>
@@ -1106,163 +1145,175 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N20" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N20" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
   <autoFilter ref="A1:N20" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{DC551193-3E78-054D-9E02-55B526E3955D}" name="Source_type" dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="86"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="85"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="83"/>
-    <tableColumn id="13" xr3:uid="{CB3B9ED9-A903-D142-8C47-DBFE1BB21BB9}" name="Communicator_role" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="81"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="72"/>
+    <tableColumn id="14" xr3:uid="{DC551193-3E78-054D-9E02-55B526E3955D}" name="Source_type" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="67"/>
+    <tableColumn id="13" xr3:uid="{CB3B9ED9-A903-D142-8C47-DBFE1BB21BB9}" name="Communicator_role" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N17" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N17" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:N17" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="72"/>
-    <tableColumn id="13" xr3:uid="{DD700407-60FC-C348-A601-E8685620E07F}" name="Source_type" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="69"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="68"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="67"/>
-    <tableColumn id="14" xr3:uid="{18CC61B1-AC23-BA4F-B2B3-2D2FB5AC969E}" name="Communicator_role" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="65"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{DD700407-60FC-C348-A601-E8685620E07F}" name="Source_type" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{18CC61B1-AC23-BA4F-B2B3-2D2FB5AC969E}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N21" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N21" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:N21" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{E398D18F-D9B1-8C4A-B81C-4F23A58404BA}" name="ID" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{41682781-F3C4-A842-B6E4-CD72DE688AF5}" name="Text" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{C1B517F2-40CD-8F40-9B4C-E34FFCCE3881}" name="Text_type" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{74E0C65C-5577-A146-9EE5-20C594C4316D}" name="Leadership_context" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{DDC33EC8-2DCC-DF43-9A08-EC991A2EA183}" name="Information_valence" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{C7BBAC6F-3D8E-B149-B9F0-D0A909FCC061}" name="Communication_type" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{DA857B5E-985B-B946-AB84-87E571EEF3AB}" name="Source_type" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{3FFDDD67-7E94-CE4D-B56E-DFAC9F1681E3}" name="Company" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{342E13F5-266B-7B42-BD6B-BB868EA49B97}" name="Country" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{69240109-8B46-AB43-AD07-1F40DB5F9C94}" name="Year" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{5ED27922-9168-D142-BBEF-32C7AE06ABD3}" name="Covid" dataDxfId="51"/>
-    <tableColumn id="13" xr3:uid="{0563ACCB-80F5-4F46-ADA0-9040F1D87085}" name="Communicator_role" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{C38872CB-C9B9-1249-9741-B341922B9857}" name="Communicator_name" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{DBF7903A-F082-FB40-B41C-987ABF6BC279}" name="Comment" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{E398D18F-D9B1-8C4A-B81C-4F23A58404BA}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{41682781-F3C4-A842-B6E4-CD72DE688AF5}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{C1B517F2-40CD-8F40-9B4C-E34FFCCE3881}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{74E0C65C-5577-A146-9EE5-20C594C4316D}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{DDC33EC8-2DCC-DF43-9A08-EC991A2EA183}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{C7BBAC6F-3D8E-B149-B9F0-D0A909FCC061}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{DA857B5E-985B-B946-AB84-87E571EEF3AB}" name="Source_type" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{3FFDDD67-7E94-CE4D-B56E-DFAC9F1681E3}" name="Company" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{342E13F5-266B-7B42-BD6B-BB868EA49B97}" name="Country" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{69240109-8B46-AB43-AD07-1F40DB5F9C94}" name="Year" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{5ED27922-9168-D142-BBEF-32C7AE06ABD3}" name="Covid" dataDxfId="35"/>
+    <tableColumn id="13" xr3:uid="{0563ACCB-80F5-4F46-ADA0-9040F1D87085}" name="Communicator_role" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{C38872CB-C9B9-1249-9741-B341922B9857}" name="Communicator_name" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{DBF7903A-F082-FB40-B41C-987ABF6BC279}" name="Comment" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{49AA2418-AB03-1149-B07A-3CC5FF67C997}" name="Tableau1345" displayName="Tableau1345" ref="A1:N24" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
-  <autoFilter ref="A1:N24" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{49AA2418-AB03-1149-B07A-3CC5FF67C997}" name="Tableau1345" displayName="Tableau1345" ref="A1:N24" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A1:N24" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="POSITIVE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{E88F34DD-82B0-AD49-8C17-D8E9CFF03D07}" name="ID" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{88FC91F1-83E8-1B40-AC59-24D584573CCF}" name="Text" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{15432912-C615-E748-A229-EAA1D750204D}" name="Text_type" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{1025B200-F152-0B42-88C1-A31B3C27DB9E}" name="Leadership_context" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{D41F3D09-61AB-B841-88C7-5242CDC613BF}" name="Information_valence" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{CE749A1F-4ED8-1C40-9BE6-FB737E09C230}" name="Communication_type" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{BDC21215-E7B5-5C4C-B5AB-80E86EA24E05}" name="Source_type" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{A6F61E0C-8D32-F54F-8B88-CFAABE31D5B0}" name="Company" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{84CFAC4D-579E-AA4B-9DFE-FB605F75FBA9}" name="Country" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{1BA4063C-1918-624B-9757-FC2F3E5A7EE2}" name="Year" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{82840B5F-FD1C-614B-9755-28207407D6E2}" name="Covid" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{3F460577-A4A9-C947-8FBE-832A71AF2E55}" name="Communicator_role" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{3C67D01C-1B28-EB45-A3B2-FA7774BA5A24}" name="Communicator_name" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{7581B405-4702-5B40-9BBE-C98F342B9125}" name="Comment" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{E88F34DD-82B0-AD49-8C17-D8E9CFF03D07}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{88FC91F1-83E8-1B40-AC59-24D584573CCF}" name="Text" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{15432912-C615-E748-A229-EAA1D750204D}" name="Text_type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{1025B200-F152-0B42-88C1-A31B3C27DB9E}" name="Leadership_context" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{D41F3D09-61AB-B841-88C7-5242CDC613BF}" name="Information_valence" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{CE749A1F-4ED8-1C40-9BE6-FB737E09C230}" name="Communication_type" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{BDC21215-E7B5-5C4C-B5AB-80E86EA24E05}" name="Source_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{A6F61E0C-8D32-F54F-8B88-CFAABE31D5B0}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{84CFAC4D-579E-AA4B-9DFE-FB605F75FBA9}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{1BA4063C-1918-624B-9757-FC2F3E5A7EE2}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{82840B5F-FD1C-614B-9755-28207407D6E2}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{3F460577-A4A9-C947-8FBE-832A71AF2E55}" name="Communicator_role" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{3C67D01C-1B28-EB45-A3B2-FA7774BA5A24}" name="Communicator_name" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{7581B405-4702-5B40-9BBE-C98F342B9125}" name="Comment" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E6C7F84-1A88-2149-AAB1-B94EF8830151}" name="Tableau13456" displayName="Tableau13456" ref="A1:N12" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A1:N12" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E6C7F84-1A88-2149-AAB1-B94EF8830151}" name="Tableau13456" displayName="Tableau13456" ref="A1:N12" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N12" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="POSITIVE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{86F19330-6E72-0543-BBCC-6D193B41E96F}" name="ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{6C469BD5-B4CF-8D4F-A2F6-F0E834902E4A}" name="Text" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{FE673CA5-CBC5-A34F-8A0C-C1CD6D144617}" name="Text_type" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{4248AFAD-ABBE-A942-8BC5-6258F7CF5E07}" name="Leadership_context" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{9D393B8E-A5EB-6240-B5FD-D449006530E5}" name="Information_valence" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{9677B29B-2D61-544A-85E3-A9C0FF7FBFCF}" name="Communication_type" dataDxfId="24"/>
-    <tableColumn id="14" xr3:uid="{5175FC7C-275C-FB4E-8512-D7A2B81AEEA9}" name="Source_type" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{9949BF20-7E90-2D45-A547-C4EF102C2AF9}" name="Company" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{5676BCFB-C3B1-444F-8A31-FAE43C2412E4}" name="Country" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{065AECA5-A4C6-784E-B897-9C586B53EEC2}" name="Year" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{9FE554FC-C9E9-BD44-8CBB-7E5AF11D1DDA}" name="Covid" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{93285A16-1AFB-F940-A523-560D3B0D9284}" name="Communicator_role" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{3C88AB16-0597-6246-B1EA-CED5E74629EC}" name="Communicator_name" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{75A6A75A-B89A-C341-99C3-8E0AF84308E5}" name="Comment" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{86F19330-6E72-0543-BBCC-6D193B41E96F}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{6C469BD5-B4CF-8D4F-A2F6-F0E834902E4A}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{FE673CA5-CBC5-A34F-8A0C-C1CD6D144617}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{4248AFAD-ABBE-A942-8BC5-6258F7CF5E07}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{9D393B8E-A5EB-6240-B5FD-D449006530E5}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{9677B29B-2D61-544A-85E3-A9C0FF7FBFCF}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{5175FC7C-275C-FB4E-8512-D7A2B81AEEA9}" name="Source_type" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{9949BF20-7E90-2D45-A547-C4EF102C2AF9}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{5676BCFB-C3B1-444F-8A31-FAE43C2412E4}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{065AECA5-A4C6-784E-B897-9C586B53EEC2}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{9FE554FC-C9E9-BD44-8CBB-7E5AF11D1DDA}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{93285A16-1AFB-F940-A523-560D3B0D9284}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{3C88AB16-0597-6246-B1EA-CED5E74629EC}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{75A6A75A-B89A-C341-99C3-8E0AF84308E5}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4E11BC3F-0045-1646-B076-F2B520D6852E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N17" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4E11BC3F-0045-1646-B076-F2B520D6852E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N17" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="A1:N17" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{31CE9BA4-76C4-7243-9CC4-2D69B48697C4}" name="ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{E9507622-53C7-7C46-AD19-75B0C284C739}" name="Text" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{B61A97EA-38E3-824E-AFFF-6DA5B0F5F799}" name="Text_type" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{C4A6AEE0-93C2-654B-AED8-9DFE0C336FBC}" name="Leadership_context" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{8B799C91-B83E-4740-8FF8-D018A500B838}" name="Information_valence" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{66E32C8C-3CF0-FF4A-8434-3DDE14801826}" name="Communication_type" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{0421BDDD-F24B-E84B-BE66-A9572A63BB7E}" name="Source_type" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{BB1E2451-7FCA-A546-B2ED-629286E517B1}" name="Company" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{A7D9EB9F-21C3-A443-AA66-25E92544A3D1}" name="Country" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{B9243626-106E-F940-9214-C16A4B219151}" name="Year" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{F1B3134A-8772-B940-A033-7567227076E7}" name="Covid" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{2561A683-C0E9-A44B-9AEB-9C3356F44833}" name="Communicator_role" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{AB9A4529-C11B-2A4B-9D39-3BBE9A62DD87}" name="Communicator_name" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{A2188241-51A1-7D40-927A-99ACD6E9501D}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{31CE9BA4-76C4-7243-9CC4-2D69B48697C4}" name="ID" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{E9507622-53C7-7C46-AD19-75B0C284C739}" name="Text" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{B61A97EA-38E3-824E-AFFF-6DA5B0F5F799}" name="Text_type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{C4A6AEE0-93C2-654B-AED8-9DFE0C336FBC}" name="Leadership_context" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{8B799C91-B83E-4740-8FF8-D018A500B838}" name="Information_valence" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{66E32C8C-3CF0-FF4A-8434-3DDE14801826}" name="Communication_type" dataDxfId="88"/>
+    <tableColumn id="13" xr3:uid="{0421BDDD-F24B-E84B-BE66-A9572A63BB7E}" name="Source_type" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{BB1E2451-7FCA-A546-B2ED-629286E517B1}" name="Company" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{A7D9EB9F-21C3-A443-AA66-25E92544A3D1}" name="Country" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{B9243626-106E-F940-9214-C16A4B219151}" name="Year" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{F1B3134A-8772-B940-A033-7567227076E7}" name="Covid" dataDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{2561A683-C0E9-A44B-9AEB-9C3356F44833}" name="Communicator_role" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{AB9A4529-C11B-2A4B-9D39-3BBE9A62DD87}" name="Communicator_name" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{A2188241-51A1-7D40-927A-99ACD6E9501D}" name="Comment" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1647,6 +1698,12 @@
       <c r="C2" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
@@ -1682,6 +1739,12 @@
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>109</v>
       </c>
@@ -1717,6 +1780,12 @@
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>109</v>
       </c>
@@ -1752,6 +1821,12 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>109</v>
       </c>
@@ -1787,6 +1862,12 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>109</v>
       </c>
@@ -1822,6 +1903,12 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>109</v>
       </c>
@@ -1857,6 +1944,12 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>109</v>
       </c>
@@ -1892,6 +1985,12 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>109</v>
       </c>
@@ -1927,6 +2026,12 @@
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>109</v>
       </c>
@@ -1962,6 +2067,12 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>109</v>
       </c>
@@ -1997,6 +2108,12 @@
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>109</v>
       </c>
@@ -2032,6 +2149,12 @@
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>109</v>
       </c>
@@ -2067,6 +2190,12 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>109</v>
       </c>
@@ -2102,6 +2231,12 @@
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>109</v>
       </c>
@@ -2137,6 +2272,12 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>109</v>
       </c>
@@ -2172,6 +2313,12 @@
       <c r="C17" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F17" s="1" t="s">
         <v>109</v>
       </c>
@@ -2207,6 +2354,12 @@
       <c r="C18" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="F18" s="1" t="s">
         <v>109</v>
       </c>
@@ -2242,6 +2395,12 @@
       <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>109</v>
       </c>
@@ -2276,6 +2435,12 @@
       </c>
       <c r="C20" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>109</v>
@@ -2382,6 +2547,12 @@
       <c r="C2" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
@@ -2417,6 +2588,12 @@
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>109</v>
       </c>
@@ -2452,6 +2629,12 @@
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>109</v>
       </c>
@@ -2487,6 +2670,12 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>109</v>
       </c>
@@ -2522,6 +2711,12 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>109</v>
       </c>
@@ -2557,6 +2752,12 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>109</v>
       </c>
@@ -2592,6 +2793,12 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>109</v>
       </c>
@@ -2627,6 +2834,12 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>109</v>
       </c>
@@ -2662,6 +2875,12 @@
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>109</v>
       </c>
@@ -2697,6 +2916,12 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>109</v>
       </c>
@@ -2732,6 +2957,12 @@
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>109</v>
       </c>
@@ -2767,6 +2998,12 @@
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>109</v>
       </c>
@@ -2802,6 +3039,12 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>109</v>
       </c>
@@ -2837,6 +3080,12 @@
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>109</v>
       </c>
@@ -2872,6 +3121,12 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>109</v>
       </c>
@@ -2906,6 +3161,12 @@
       </c>
       <c r="C17" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>109</v>
@@ -3012,6 +3273,12 @@
       <c r="C2" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
@@ -3047,6 +3314,12 @@
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>109</v>
       </c>
@@ -3082,6 +3355,12 @@
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>109</v>
       </c>
@@ -3107,7 +3386,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="204" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>177</v>
       </c>
@@ -3116,6 +3395,12 @@
       </c>
       <c r="C5" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>109</v>
@@ -3152,6 +3437,12 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>109</v>
       </c>
@@ -3187,6 +3478,12 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>109</v>
       </c>
@@ -3222,6 +3519,12 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>109</v>
       </c>
@@ -3257,6 +3560,12 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>109</v>
       </c>
@@ -3292,6 +3601,12 @@
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>109</v>
       </c>
@@ -3327,6 +3642,12 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>109</v>
       </c>
@@ -3362,6 +3683,12 @@
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>109</v>
       </c>
@@ -3397,6 +3724,12 @@
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>109</v>
       </c>
@@ -3432,6 +3765,12 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>109</v>
       </c>
@@ -3467,6 +3806,12 @@
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>109</v>
       </c>
@@ -3502,6 +3847,12 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>109</v>
       </c>
@@ -3537,6 +3888,12 @@
       <c r="C17" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F17" s="1" t="s">
         <v>109</v>
       </c>
@@ -3572,6 +3929,12 @@
       <c r="C18" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F18" s="1" t="s">
         <v>109</v>
       </c>
@@ -3607,6 +3970,12 @@
       <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>109</v>
       </c>
@@ -3642,6 +4011,12 @@
       <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F20" s="1" t="s">
         <v>109</v>
       </c>
@@ -3676,6 +4051,12 @@
       </c>
       <c r="C21" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>109</v>
@@ -3782,6 +4163,12 @@
       <c r="C2" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
@@ -3817,6 +4204,12 @@
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>109</v>
       </c>
@@ -3852,6 +4245,12 @@
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>109</v>
       </c>
@@ -3887,6 +4286,12 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>109</v>
       </c>
@@ -3922,6 +4327,12 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>109</v>
       </c>
@@ -3957,6 +4368,12 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>109</v>
       </c>
@@ -3982,7 +4399,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>159</v>
       </c>
@@ -3991,6 +4408,12 @@
       </c>
       <c r="C8" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>109</v>
@@ -4027,6 +4450,12 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>109</v>
       </c>
@@ -4062,6 +4491,12 @@
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>109</v>
       </c>
@@ -4097,6 +4532,12 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>109</v>
       </c>
@@ -4122,7 +4563,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>163</v>
       </c>
@@ -4131,6 +4572,12 @@
       </c>
       <c r="C12" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>109</v>
@@ -4167,6 +4614,12 @@
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>109</v>
       </c>
@@ -4202,6 +4655,12 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>109</v>
       </c>
@@ -4237,6 +4696,12 @@
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>109</v>
       </c>
@@ -4272,6 +4737,12 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F16" s="1" t="s">
         <v>109</v>
       </c>
@@ -4307,6 +4778,12 @@
       <c r="C17" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F17" s="1" t="s">
         <v>109</v>
       </c>
@@ -4342,6 +4819,12 @@
       <c r="C18" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F18" s="1" t="s">
         <v>109</v>
       </c>
@@ -4377,6 +4860,12 @@
       <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F19" s="1" t="s">
         <v>109</v>
       </c>
@@ -4412,6 +4901,12 @@
       <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F20" s="1" t="s">
         <v>109</v>
       </c>
@@ -4447,6 +4942,12 @@
       <c r="C21" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F21" s="1" t="s">
         <v>109</v>
       </c>
@@ -4482,6 +4983,12 @@
       <c r="C22" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D22" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F22" s="1" t="s">
         <v>109</v>
       </c>
@@ -4517,6 +5024,12 @@
       <c r="C23" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F23" s="1" t="s">
         <v>109</v>
       </c>
@@ -4542,7 +5055,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>228</v>
       </c>
@@ -4551,6 +5064,12 @@
       </c>
       <c r="C24" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>109</v>
@@ -4657,6 +5176,12 @@
       <c r="C2" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
@@ -4692,6 +5217,12 @@
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>109</v>
       </c>
@@ -4717,7 +5248,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>132</v>
       </c>
@@ -4726,6 +5257,12 @@
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>109</v>
@@ -4762,6 +5299,12 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>109</v>
       </c>
@@ -4797,6 +5340,12 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>109</v>
       </c>
@@ -4832,6 +5381,12 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>109</v>
       </c>
@@ -4867,6 +5422,12 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>109</v>
       </c>
@@ -4892,7 +5453,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="170" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>137</v>
       </c>
@@ -4902,6 +5463,12 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>109</v>
       </c>
@@ -4927,7 +5494,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>138</v>
       </c>
@@ -4936,6 +5503,12 @@
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>109</v>
@@ -4972,6 +5545,12 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>109</v>
       </c>
@@ -4997,7 +5576,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>229</v>
       </c>
@@ -5006,6 +5585,12 @@
       </c>
       <c r="C12" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>109</v>
@@ -5112,6 +5697,12 @@
       <c r="C2" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
@@ -5147,6 +5738,12 @@
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>109</v>
       </c>
@@ -5182,6 +5779,12 @@
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>109</v>
       </c>
@@ -5217,6 +5820,12 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>109</v>
       </c>
@@ -5252,6 +5861,12 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>109</v>
       </c>
@@ -5287,6 +5902,12 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>109</v>
       </c>
@@ -5322,6 +5943,12 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>109</v>
       </c>
@@ -5357,6 +5984,12 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>109</v>
       </c>
@@ -5392,6 +6025,12 @@
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>109</v>
       </c>
@@ -5427,6 +6066,12 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>109</v>
       </c>
@@ -5452,7 +6097,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>149</v>
       </c>
@@ -5462,6 +6107,12 @@
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>109</v>
       </c>
@@ -5487,7 +6138,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>150</v>
       </c>
@@ -5496,6 +6147,12 @@
       </c>
       <c r="C13" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>109</v>
@@ -5532,6 +6189,12 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>109</v>
       </c>
@@ -5567,6 +6230,12 @@
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>109</v>
       </c>
@@ -5592,7 +6261,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>153</v>
       </c>
@@ -5601,6 +6270,12 @@
       </c>
       <c r="C16" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>109</v>
@@ -5636,6 +6311,12 @@
       </c>
       <c r="C17" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>109</v>
